--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1469,17 +1469,17 @@
   <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.19921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.84375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.94140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="31.81640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="28.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1488,25 +1488,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="193.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="95.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="173.4453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="85.84375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-10T12:52:28-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:52:28-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T21:50:44-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:50:44-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-18T15:36:33-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -706,7 +706,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -930,7 +930,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -967,7 +967,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1043,7 +1043,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1479,7 +1479,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="30.03515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="38.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:36:33-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
+++ b/build/output/StructureDefinition-cibmtr-gvhd-prophylaxis-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -706,7 +706,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -867,7 +867,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.8/expansion</t>
+    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/med-gvhd-prophylaxis-vs</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -930,7 +930,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -967,7 +967,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1043,7 +1043,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1479,7 +1479,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="30.03515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="38.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1494,7 +1494,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.6875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
